--- a/exports/AXISBANK_full_report.xlsx
+++ b/exports/AXISBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.44</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44575.55208333334</v>
+        <v>44578.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>721.25</v>
+        <v>711</v>
       </c>
       <c r="I2" t="n">
         <v>718.5742135</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.41</v>
+        <v>-3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>3.11</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>0.76</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>4.85</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44585.55208333334</v>
+        <v>44586.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>703.8</v>
+        <v>744.85</v>
       </c>
       <c r="I3" t="n">
         <v>737.0495006190417</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.01</v>
+        <v>-4.76</v>
       </c>
       <c r="L3" t="n">
-        <v>3.61</v>
+        <v>5.39</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.45</v>
       </c>
       <c r="N3" t="n">
-        <v>1.79</v>
+        <v>6.65</v>
       </c>
       <c r="O3" t="n">
         <v>-1.2</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.68</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>783.3</v>
+        <v>772</v>
       </c>
       <c r="I4" t="n">
         <v>773.4709833898315</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>5.16</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>4.85</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.68</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44635.55208333334</v>
+        <v>44636.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>695.5</v>
+        <v>720.1</v>
       </c>
       <c r="I5" t="n">
         <v>718.9056273223149</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>9.91</v>
+        <v>6.72</v>
       </c>
       <c r="L5" t="n">
         <v>4.7</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.51</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44677.55208333334</v>
+        <v>44678.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>776.7</v>
+        <v>750.15</v>
       </c>
       <c r="I6" t="n">
         <v>767.9333274873557</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K6" t="n">
-        <v>7.86</v>
+        <v>4.17</v>
       </c>
       <c r="L6" t="n">
         <v>1.9</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.01</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>687.95</v>
+        <v>694.6</v>
       </c>
       <c r="I7" t="n">
         <v>689.4900329861273</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K7" t="n">
-        <v>8.289999999999999</v>
+        <v>7.41</v>
       </c>
       <c r="L7" t="n">
         <v>4.68</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>5.05</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44720.38541666666</v>
+        <v>44720.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>662.55</v>
+        <v>658.55</v>
       </c>
       <c r="I8" t="n">
         <v>661.6278436062137</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.61</v>
+        <v>-5.19</v>
       </c>
       <c r="L8" t="n">
-        <v>4.82</v>
+        <v>5.63</v>
       </c>
       <c r="M8" t="n">
         <v>0.87</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>4.59</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44747.55208333334</v>
+        <v>44748.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>647.25</v>
+        <v>658.9</v>
       </c>
       <c r="I9" t="n">
         <v>656.982568649637</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>1.72</v>
+        <v>-0.05</v>
       </c>
       <c r="L9" t="n">
         <v>0.77</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.06</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>754.6</v>
+        <v>742.05</v>
       </c>
       <c r="I10" t="n">
         <v>743.7440615159687</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K10" t="n">
-        <v>14.52</v>
+        <v>12.62</v>
       </c>
       <c r="L10" t="n">
         <v>1.1</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>4.96</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44811.55208333334</v>
+        <v>44812.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>754</v>
+        <v>771.3</v>
       </c>
       <c r="I11" t="n">
         <v>761.2491300173425</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.61</v>
+        <v>-3.94</v>
       </c>
       <c r="L11" t="n">
-        <v>2.63</v>
+        <v>4.49</v>
       </c>
       <c r="M11" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>2.99</v>
+        <v>3.67</v>
       </c>
       <c r="O11" t="n">
         <v>-1.32</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.09</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>789.8</v>
+        <v>767.8</v>
       </c>
       <c r="I12" t="n">
         <v>778.9899149742635</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>-0.45</v>
       </c>
       <c r="L12" t="n">
         <v>1.77</v>
@@ -1125,7 +1268,7 @@
         <v>1.58</v>
       </c>
       <c r="N12" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
         <v>3.67</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.29</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44841.55208333334</v>
+        <v>44844.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>756.95</v>
+        <v>770.1</v>
       </c>
       <c r="I13" t="n">
         <v>764.2591856737899</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>1.41</v>
+        <v>-0.3</v>
       </c>
       <c r="L13" t="n">
         <v>2.76</v>
@@ -1182,7 +1337,7 @@
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="O13" t="n">
         <v>-2.7</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.2</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44866.55208333334</v>
+        <v>44867.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>871.5</v>
+        <v>864.65</v>
       </c>
       <c r="I14" t="n">
         <v>865.3217268490231</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>13.17</v>
+        <v>12.28</v>
       </c>
       <c r="L14" t="n">
         <v>3.26</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.06</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44889.55208333334</v>
+        <v>44890.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>880.8</v>
+        <v>887.55</v>
       </c>
       <c r="I15" t="n">
         <v>883.4457996528812</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.87</v>
+        <v>-2.65</v>
       </c>
       <c r="L15" t="n">
-        <v>1.87</v>
+        <v>3.14</v>
       </c>
       <c r="M15" t="n">
         <v>0.93</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>2.81</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>917.65</v>
+        <v>909.1</v>
       </c>
       <c r="I16" t="n">
         <v>916.873679812383</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K16" t="n">
-        <v>3.39</v>
+        <v>2.43</v>
       </c>
       <c r="L16" t="n">
         <v>0.75</v>
       </c>
       <c r="M16" t="n">
-        <v>0.45</v>
+        <v>0.62</v>
       </c>
       <c r="N16" t="n">
         <v>2.16</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>4.25</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44928.38541666666</v>
+        <v>44928.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>937.45</v>
+        <v>944.95</v>
       </c>
       <c r="I17" t="n">
         <v>941.329258307586</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.12</v>
+        <v>-3.94</v>
       </c>
       <c r="L17" t="n">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="M17" t="n">
         <v>0.35</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>4.51</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44937.55208333334</v>
+        <v>44938.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>949.3</v>
+        <v>927.4</v>
       </c>
       <c r="I18" t="n">
         <v>929.0820943240866</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K18" t="n">
-        <v>0.46</v>
+        <v>-1.86</v>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>1.99</v>
       </c>
       <c r="M18" t="n">
         <v>0.26</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>1.51</v>
       </c>
       <c r="O18" t="n">
         <v>1.07</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.54</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44993.55208333334</v>
+        <v>44994.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>861.3</v>
+        <v>871.9</v>
       </c>
       <c r="I19" t="n">
         <v>865.9615790209452</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K19" t="n">
-        <v>7.13</v>
+        <v>5.98</v>
       </c>
       <c r="L19" t="n">
         <v>2.39</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>3.99</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>850.6</v>
+        <v>838.55</v>
       </c>
       <c r="I20" t="n">
         <v>838.5939861735875</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.44</v>
+        <v>-3.82</v>
       </c>
       <c r="L20" t="n">
-        <v>3.02</v>
+        <v>3.83</v>
       </c>
       <c r="M20" t="n">
         <v>0.62</v>
       </c>
       <c r="N20" t="n">
-        <v>1.66</v>
+        <v>2.19</v>
       </c>
       <c r="O20" t="n">
         <v>0.43</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>5.18</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>858.7</v>
+        <v>865.35</v>
       </c>
       <c r="I21" t="n">
         <v>859.4731512540772</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.4</v>
+        <v>-3.2</v>
       </c>
       <c r="L21" t="n">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.24</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45043.55208333334</v>
+        <v>45044.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>880.5</v>
+        <v>855.7</v>
       </c>
       <c r="I22" t="n">
         <v>856.4557825762204</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>1.75</v>
+        <v>-1.12</v>
       </c>
       <c r="L22" t="n">
         <v>2.47</v>
@@ -1695,7 +1958,7 @@
         <v>0.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.16</v>
+        <v>2.33</v>
       </c>
       <c r="O22" t="n">
         <v>0.96</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>6.45</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45056.55208333334</v>
+        <v>45057.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>890</v>
+        <v>897.4</v>
       </c>
       <c r="I23" t="n">
         <v>894.1904754695371</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.01</v>
+        <v>-4.87</v>
       </c>
       <c r="L23" t="n">
-        <v>4.3</v>
+        <v>5.04</v>
       </c>
       <c r="M23" t="n">
         <v>1.17</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>3.91</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45076.55208333334</v>
+        <v>45077.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>935.15</v>
+        <v>911.35</v>
       </c>
       <c r="I24" t="n">
         <v>911.7463516103891</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K24" t="n">
-        <v>4.21</v>
+        <v>1.55</v>
       </c>
       <c r="L24" t="n">
         <v>0.92</v>
@@ -1809,7 +2096,7 @@
         <v>0.31</v>
       </c>
       <c r="N24" t="n">
-        <v>0.98</v>
+        <v>1.89</v>
       </c>
       <c r="O24" t="n">
         <v>0.64</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>4.93</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45079.55208333334</v>
+        <v>45082.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>923.7</v>
+        <v>949.6</v>
       </c>
       <c r="I25" t="n">
         <v>944.0852051955848</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.36</v>
+        <v>-4.2</v>
       </c>
       <c r="L25" t="n">
-        <v>3.11</v>
+        <v>4.33</v>
       </c>
       <c r="M25" t="n">
         <v>0.49</v>
       </c>
       <c r="N25" t="n">
-        <v>0.44</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
         <v>-1.89</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.8</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45118.38541666666</v>
+        <v>45118.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>962.1</v>
+        <v>955</v>
       </c>
       <c r="I26" t="n">
         <v>957.4723912662176</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>1.32</v>
+        <v>0.57</v>
       </c>
       <c r="L26" t="n">
         <v>2.32</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>3.97</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45160.55208333334</v>
+        <v>45161.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>958</v>
+        <v>976.45</v>
       </c>
       <c r="I27" t="n">
         <v>964.8919341985505</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.31</v>
+        <v>-2.25</v>
       </c>
       <c r="L27" t="n">
         <v>3.66</v>
@@ -1980,7 +2303,7 @@
         <v>1.54</v>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="O27" t="n">
         <v>-1</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>3.96</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45202.55208333334</v>
+        <v>45203.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1038.5</v>
+        <v>1002.1</v>
       </c>
       <c r="I28" t="n">
         <v>1008.560308250394</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K28" t="n">
-        <v>6.35</v>
+        <v>2.63</v>
       </c>
       <c r="L28" t="n">
         <v>1.85</v>
@@ -2037,7 +2372,7 @@
         <v>1.02</v>
       </c>
       <c r="N28" t="n">
-        <v>1.44</v>
+        <v>4.59</v>
       </c>
       <c r="O28" t="n">
         <v>2.01</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>5.7</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45226.38541666666</v>
+        <v>45226.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>985.65</v>
+        <v>999.9</v>
       </c>
       <c r="I29" t="n">
         <v>996.8569514966235</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>1.64</v>
+        <v>0.22</v>
       </c>
       <c r="L29" t="n">
         <v>3.48</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>4.81</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45246.55208333334</v>
+        <v>45247.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1026</v>
+        <v>994.85</v>
       </c>
       <c r="I30" t="n">
         <v>1008.190608066972</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>2.61</v>
+        <v>-0.51</v>
       </c>
       <c r="L30" t="n">
         <v>3.19</v>
       </c>
       <c r="M30" t="n">
-        <v>0.33</v>
+        <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>1.49</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>2.73</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>5.06</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45258.55208333334</v>
+        <v>45259.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1019.2</v>
+        <v>1044.9</v>
       </c>
       <c r="I31" t="n">
         <v>1024.339469501611</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.45</v>
+        <v>-5.03</v>
       </c>
       <c r="L31" t="n">
-        <v>2.72</v>
+        <v>5.03</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4</v>
+        <v>0.78</v>
       </c>
       <c r="N31" t="n">
-        <v>1.01</v>
+        <v>3.74</v>
       </c>
       <c r="O31" t="n">
         <v>-3.25</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.22</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45292.55208333334</v>
+        <v>45293.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1095</v>
+        <v>1083.45</v>
       </c>
       <c r="I32" t="n">
         <v>1083.740705280634</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K32" t="n">
-        <v>4.79</v>
+        <v>3.69</v>
       </c>
       <c r="L32" t="n">
         <v>2.27</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>4.3</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45294.55208333334</v>
+        <v>45295.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1098</v>
+        <v>1129.5</v>
       </c>
       <c r="I33" t="n">
         <v>1128.133589086985</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.34</v>
+        <v>-4.25</v>
       </c>
       <c r="L33" t="n">
-        <v>1.77</v>
+        <v>4.3</v>
       </c>
       <c r="M33" t="n">
-        <v>0.13</v>
+        <v>0.46</v>
       </c>
       <c r="N33" t="n">
-        <v>0.78</v>
+        <v>2.46</v>
       </c>
       <c r="O33" t="n">
         <v>-0.5</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>5.2</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45307.55208333334</v>
+        <v>45308.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1120.2</v>
+        <v>1092.35</v>
       </c>
       <c r="I34" t="n">
         <v>1093.549320813821</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.82</v>
+        <v>-3.29</v>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>4.32</v>
       </c>
       <c r="M34" t="n">
-        <v>0.34</v>
+        <v>3.41</v>
       </c>
       <c r="N34" t="n">
-        <v>1.08</v>
+        <v>3.45</v>
       </c>
       <c r="O34" t="n">
         <v>2.46</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>4.69</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45344.38541666666</v>
+        <v>45344.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>1085.65</v>
+        <v>1098.75</v>
       </c>
       <c r="I35" t="n">
         <v>1097.59127804821</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>0.61</v>
+        <v>-0.59</v>
       </c>
       <c r="L35" t="n">
         <v>4.51</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.35</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1094.45</v>
+        <v>1076.2</v>
       </c>
       <c r="I36" t="n">
         <v>1078.927865021964</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.39</v>
+        <v>-2.05</v>
       </c>
       <c r="L36" t="n">
         <v>3.95</v>
@@ -2493,7 +2924,7 @@
         <v>0.28</v>
       </c>
       <c r="N36" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="O36" t="n">
         <v>1.78</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.85</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45391.55208333334</v>
+        <v>45392.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1079.95</v>
+        <v>1085.2</v>
       </c>
       <c r="I37" t="n">
         <v>1084.258333514649</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.35</v>
+        <v>-0.84</v>
       </c>
       <c r="L37" t="n">
         <v>2.17</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>3.69</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45398.55208333334</v>
+        <v>45400.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1055.9</v>
+        <v>1037.6</v>
       </c>
       <c r="I38" t="n">
         <v>1047.819969779708</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.7</v>
+        <v>-4.39</v>
       </c>
       <c r="L38" t="n">
-        <v>3.76</v>
+        <v>4.83</v>
       </c>
       <c r="M38" t="n">
-        <v>0.84</v>
+        <v>1.11</v>
       </c>
       <c r="N38" t="n">
-        <v>1.34</v>
+        <v>2.85</v>
       </c>
       <c r="O38" t="n">
         <v>0.41</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>4.37</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45405.55208333334</v>
+        <v>45406.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1055</v>
+        <v>1064.85</v>
       </c>
       <c r="I39" t="n">
         <v>1055.455692552705</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.68</v>
+        <v>-2.63</v>
       </c>
       <c r="L39" t="n">
-        <v>2.18</v>
+        <v>3.02</v>
       </c>
       <c r="M39" t="n">
         <v>0.76</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>4.68</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1228.5</v>
+        <v>1142.8</v>
       </c>
       <c r="I40" t="n">
         <v>1150.857521170929</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K40" t="n">
-        <v>15.37</v>
+        <v>7.32</v>
       </c>
       <c r="L40" t="n">
         <v>0.83</v>
@@ -2721,7 +3200,7 @@
         <v>0.88</v>
       </c>
       <c r="N40" t="n">
-        <v>1.47</v>
+        <v>7.37</v>
       </c>
       <c r="O40" t="n">
         <v>0.95</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>10.45</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45467.55208333334</v>
+        <v>45468.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1229.5</v>
+        <v>1263.85</v>
       </c>
       <c r="I41" t="n">
         <v>1241.096667066393</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.59</v>
+        <v>-10.59</v>
       </c>
       <c r="L41" t="n">
-        <v>9.029999999999999</v>
+        <v>10.61</v>
       </c>
       <c r="M41" t="n">
         <v>1.33</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.05</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1286.2</v>
+        <v>1253.15</v>
       </c>
       <c r="I42" t="n">
         <v>1260.432570096152</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K42" t="n">
-        <v>1.77</v>
+        <v>-0.85</v>
       </c>
       <c r="L42" t="n">
         <v>2.99</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.79</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45537.38541666666</v>
+        <v>45537.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1182.2</v>
+        <v>1189</v>
       </c>
       <c r="I43" t="n">
         <v>1184.243082058534</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>5.66</v>
+        <v>5.12</v>
       </c>
       <c r="L43" t="n">
         <v>3.03</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>2.77</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45566.38541666666</v>
+        <v>45566.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1234.6</v>
+        <v>1227.5</v>
       </c>
       <c r="I44" t="n">
         <v>1229.888667450073</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K44" t="n">
-        <v>3.84</v>
+        <v>3.24</v>
       </c>
       <c r="L44" t="n">
         <v>3.7</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>4.11</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45582.55208333334</v>
+        <v>45583.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1131</v>
+        <v>1197.35</v>
       </c>
       <c r="I45" t="n">
         <v>1178.678488776401</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>7.86</v>
+        <v>2.46</v>
       </c>
       <c r="L45" t="n">
         <v>0.58</v>
       </c>
       <c r="M45" t="n">
-        <v>0.58</v>
+        <v>2.39</v>
       </c>
       <c r="N45" t="n">
-        <v>1.15</v>
+        <v>5.83</v>
       </c>
       <c r="O45" t="n">
         <v>-0.33</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>7.04</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45610.55208333334</v>
+        <v>45614.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1141.5</v>
+        <v>1125.8</v>
       </c>
       <c r="I46" t="n">
         <v>1135.767331682004</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.66</v>
+        <v>-5.98</v>
       </c>
       <c r="L46" t="n">
-        <v>5.49</v>
+        <v>6.33</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="N46" t="n">
         <v>2.2</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>4.84</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45631.55208333334</v>
+        <v>45632.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1168.5</v>
+        <v>1190.8</v>
       </c>
       <c r="I47" t="n">
         <v>1172.49417433133</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.79</v>
+        <v>-5.77</v>
       </c>
       <c r="L47" t="n">
-        <v>4.54</v>
+        <v>6.04</v>
       </c>
       <c r="M47" t="n">
         <v>1.59</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>5.34</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45638.55208333334</v>
+        <v>45639.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1145</v>
+        <v>1134.7</v>
       </c>
       <c r="I48" t="n">
         <v>1139.07641412813</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.85</v>
+        <v>-4.71</v>
       </c>
       <c r="L48" t="n">
-        <v>3.96</v>
+        <v>6.48</v>
       </c>
       <c r="M48" t="n">
         <v>0.93</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>3.54</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45684.55208333334</v>
+        <v>45685.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>947.55</v>
+        <v>991.65</v>
       </c>
       <c r="I49" t="n">
         <v>984.5907274472963</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K49" t="n">
-        <v>16.49</v>
+        <v>12.61</v>
       </c>
       <c r="L49" t="n">
         <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>0.83</v>
+        <v>1.31</v>
       </c>
       <c r="N49" t="n">
-        <v>1.81</v>
+        <v>3.77</v>
       </c>
       <c r="O49" t="n">
         <v>0.67</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.9</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45702.55208333334</v>
+        <v>45705.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>996</v>
+        <v>981.3</v>
       </c>
       <c r="I50" t="n">
         <v>984.6563219964684</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>0.44</v>
+        <v>-1.04</v>
       </c>
       <c r="L50" t="n">
         <v>3.37</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>5.32</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1014.25</v>
+        <v>1033.3</v>
       </c>
       <c r="I51" t="n">
         <v>1032.533226631815</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.36</v>
+        <v>-5.3</v>
       </c>
       <c r="L51" t="n">
-        <v>5.52</v>
+        <v>5.93</v>
       </c>
       <c r="M51" t="n">
-        <v>0.14</v>
+        <v>0.82</v>
       </c>
       <c r="N51" t="n">
-        <v>1.46</v>
+        <v>1.95</v>
       </c>
       <c r="O51" t="n">
         <v>-0.1</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>4.7</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1090.1</v>
+        <v>1037</v>
       </c>
       <c r="I52" t="n">
         <v>1063.062369678245</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K52" t="n">
-        <v>5.5</v>
+        <v>0.36</v>
       </c>
       <c r="L52" t="n">
         <v>3.3</v>
       </c>
       <c r="M52" t="n">
-        <v>0.73</v>
+        <v>5.05</v>
       </c>
       <c r="N52" t="n">
-        <v>1.51</v>
+        <v>3.51</v>
       </c>
       <c r="O52" t="n">
         <v>1.95</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.16</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1068.75</v>
+        <v>1111.8</v>
       </c>
       <c r="I53" t="n">
         <v>1103.812524988381</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.06</v>
+        <v>-7.21</v>
       </c>
       <c r="L53" t="n">
-        <v>4.62</v>
+        <v>7.43</v>
       </c>
       <c r="M53" t="n">
-        <v>0.87</v>
+        <v>1.99</v>
       </c>
       <c r="N53" t="n">
-        <v>2.49</v>
+        <v>4.37</v>
       </c>
       <c r="O53" t="n">
         <v>-3.51</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.69</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45786.38541666666</v>
+        <v>45786.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1156.5</v>
+        <v>1153</v>
       </c>
       <c r="I54" t="n">
         <v>1155.275233735239</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>4.02</v>
+        <v>3.71</v>
       </c>
       <c r="L54" t="n">
         <v>2.59</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>4.01</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1195.9</v>
+        <v>1204.5</v>
       </c>
       <c r="I55" t="n">
         <v>1199.212770011313</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.72</v>
+        <v>-4.47</v>
       </c>
       <c r="L55" t="n">
-        <v>4.29</v>
+        <v>4.86</v>
       </c>
       <c r="M55" t="n">
         <v>2.78</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>4.75</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45811.55208333334</v>
+        <v>45812.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1180.7</v>
+        <v>1173.5</v>
       </c>
       <c r="I56" t="n">
         <v>1174.738203048882</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.98</v>
+        <v>-2.57</v>
       </c>
       <c r="L56" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="M56" t="n">
         <v>0.63</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>4.41</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45814.55208333334</v>
+        <v>45817.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1195.5</v>
+        <v>1221.2</v>
       </c>
       <c r="I57" t="n">
         <v>1201.484088259635</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.87</v>
+        <v>-4.06</v>
       </c>
       <c r="L57" t="n">
-        <v>2.36</v>
+        <v>4.35</v>
       </c>
       <c r="M57" t="n">
-        <v>0.09</v>
+        <v>1.42</v>
       </c>
       <c r="N57" t="n">
         <v>3.06</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>4.68</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45838.55208333334</v>
+        <v>45839.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1199</v>
+        <v>1171</v>
       </c>
       <c r="I58" t="n">
         <v>1193.211894687272</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.82</v>
+        <v>-4.11</v>
       </c>
       <c r="L58" t="n">
-        <v>2.3</v>
+        <v>4.44</v>
       </c>
       <c r="M58" t="n">
         <v>1.16</v>
       </c>
       <c r="N58" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="O58" t="n">
         <v>2.09</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.52</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45910.55208333334</v>
+        <v>45911.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1073</v>
+        <v>1087.6</v>
       </c>
       <c r="I59" t="n">
         <v>1079.51879713826</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>71.16666666666667</v>
+        <v>72</v>
       </c>
       <c r="K59" t="n">
-        <v>8.369999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="L59" t="n">
         <v>2.65</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>3.8</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45930.38541666666</v>
+        <v>45930.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>1133.6</v>
+        <v>1131</v>
       </c>
       <c r="I60" t="n">
         <v>1131.858323637235</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>4.23</v>
+        <v>3.99</v>
       </c>
       <c r="L60" t="n">
         <v>1.71</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>3.45</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45931.55208333334</v>
+        <v>45933.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1161.4</v>
+        <v>1174.9</v>
       </c>
       <c r="I61" t="n">
         <v>1169.997095977133</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.69</v>
+        <v>-3.88</v>
       </c>
       <c r="L61" t="n">
-        <v>2.99</v>
+        <v>5.04</v>
       </c>
       <c r="M61" t="n">
-        <v>0.13</v>
+        <v>0.83</v>
       </c>
       <c r="N61" t="n">
         <v>2.69</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>3.58</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46006.55208333334</v>
+        <v>46007.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1284.4</v>
+        <v>1230.3</v>
       </c>
       <c r="I62" t="n">
         <v>1252.127276340046</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>73.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K62" t="n">
-        <v>9.32</v>
+        <v>4.72</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -3975,7 +4718,7 @@
         <v>0.97</v>
       </c>
       <c r="N62" t="n">
-        <v>1.66</v>
+        <v>5.15</v>
       </c>
       <c r="O62" t="n">
         <v>1.86</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.61</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46021.55208333334</v>
+        <v>46022.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1246</v>
+        <v>1265.8</v>
       </c>
       <c r="I63" t="n">
         <v>1257.154650110982</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.28</v>
+        <v>-2.89</v>
       </c>
       <c r="L63" t="n">
         <v>3.84</v>
@@ -4032,7 +4787,7 @@
         <v>0.54</v>
       </c>
       <c r="N63" t="n">
-        <v>1.05</v>
+        <v>1.82</v>
       </c>
       <c r="O63" t="n">
         <v>-5.15</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>3.57</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46045.38541666666</v>
+        <v>46045.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>1275.9</v>
+        <v>1253.9</v>
       </c>
       <c r="I64" t="n">
         <v>1258.497860744635</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>0.8</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L64" t="n">
         <v>1.64</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.29</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46049.38541666666</v>
+        <v>46049.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>1312.9</v>
+        <v>1322</v>
       </c>
       <c r="I65" t="n">
         <v>1320.22841591981</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.71</v>
+        <v>-5.43</v>
       </c>
       <c r="L65" t="n">
         <v>6.32</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>5.75</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1367.2</v>
+        <v>1336.5</v>
       </c>
       <c r="I66" t="n">
         <v>1352.647790141836</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>34</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K66" t="n">
-        <v>3.42</v>
+        <v>1.1</v>
       </c>
       <c r="L66" t="n">
         <v>1.44</v>
       </c>
       <c r="M66" t="n">
-        <v>1.08</v>
+        <v>1.66</v>
       </c>
       <c r="N66" t="n">
         <v>3.02</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>4.53</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46118.38541666666</v>
+        <v>46118.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>1229.7</v>
+        <v>1240.4</v>
       </c>
       <c r="I67" t="n">
         <v>1237.319215271524</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K67" t="n">
-        <v>7.99</v>
+        <v>7.19</v>
       </c>
       <c r="L67" t="n">
         <v>1.58</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.95</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46139.55208333334</v>
+        <v>46140.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1325.3</v>
+        <v>1291.6</v>
       </c>
       <c r="I68" t="n">
         <v>1319.796878055729</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K68" t="n">
-        <v>6.84</v>
+        <v>4.13</v>
       </c>
       <c r="L68" t="n">
         <v>1.56</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.66</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>1287</v>
+        <v>1305.3</v>
       </c>
       <c r="I69" t="n">
         <v>1293.985464721818</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K69" t="n">
-        <v>0.36</v>
+        <v>-1.06</v>
       </c>
       <c r="L69" t="n">
         <v>2.31</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>4.63</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46175.38541666666</v>
+        <v>46175.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>1262.4</v>
+        <v>1253.4</v>
       </c>
       <c r="I70" t="n">
         <v>1255.174323408983</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.29</v>
+        <v>-3.98</v>
       </c>
       <c r="L70" t="n">
         <v>4.63</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>4.81</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46182.55208333334</v>
+        <v>46183.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>1294.4</v>
+        <v>1324</v>
       </c>
       <c r="I71" t="n">
         <v>1302.912447589352</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.27</v>
+        <v>-5.63</v>
       </c>
       <c r="L71" t="n">
-        <v>3.59</v>
+        <v>5.83</v>
       </c>
       <c r="M71" t="n">
         <v>0.6899999999999999</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>6.07</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46206.38541666666</v>
+        <v>46206.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>1353</v>
+        <v>1342</v>
       </c>
       <c r="I72" t="n">
         <v>1344.326486226681</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K72" t="n">
-        <v>2.19</v>
+        <v>1.36</v>
       </c>
       <c r="L72" t="n">
         <v>3.06</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>4.23</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46259.55208333334</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>1234.8</v>
+        <v>1257.5</v>
       </c>
       <c r="I73" t="n">
         <v>1248.196462079624</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>53</v>
+        <v>53.83333333333334</v>
       </c>
       <c r="K73" t="n">
-        <v>7.99</v>
+        <v>6.3</v>
       </c>
       <c r="L73" t="n">
         <v>2.16</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>3.78</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46276.55208333334</v>
+        <v>46280.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>1251.1</v>
+        <v>1233</v>
       </c>
       <c r="I74" t="n">
         <v>1236.72048809704</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.51</v>
+        <v>-1.95</v>
       </c>
       <c r="L74" t="n">
         <v>2.2</v>
@@ -4659,7 +5546,7 @@
         <v>0.71</v>
       </c>
       <c r="N74" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="O74" t="n">
         <v>1.71</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,25 +5594,25 @@
         <v>4.41</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>1224</v>
+        <v>1250.3</v>
       </c>
       <c r="I75" t="n">
         <v>1236.315996518116</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K75" t="n">
-        <v>0.73</v>
+        <v>-1.4</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
       </c>
       <c r="M75" t="n">
-        <v>0.47</v>
+        <v>0.82</v>
       </c>
       <c r="N75" t="n">
         <v>2.42</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>5.21</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>1236.5</v>
+        <v>1206.9</v>
       </c>
       <c r="I76" t="n">
         <v>1232.696607532563</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K76" t="n">
-        <v>-1.1</v>
+        <v>-3.47</v>
       </c>
       <c r="L76" t="n">
-        <v>2</v>
+        <v>3.49</v>
       </c>
       <c r="M76" t="n">
         <v>1.76</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,14 @@
       <c r="Q77" t="n">
         <v>12</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6935,7 +7866,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="6">
@@ -6945,7 +7876,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6955,7 +7886,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>73.2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -6965,7 +7896,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6975,7 +7906,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.9</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="10">
@@ -6985,7 +7916,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41.2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -6995,7 +7926,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -7005,7 +7936,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -7015,7 +7946,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.3</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="14">
@@ -7025,7 +7956,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.69</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="15">
@@ -7035,7 +7966,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="16">
@@ -7045,7 +7976,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.85</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="17">
@@ -7055,7 +7986,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.49</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="18">
@@ -7065,7 +7996,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.7</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="19">
@@ -7075,7 +8006,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.95</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="20">
@@ -7085,7 +8016,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="21">
@@ -7095,7 +8026,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.029999999999999</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="22">
@@ -7105,7 +8036,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -7115,7 +8046,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -7125,7 +8056,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="25">
@@ -7135,7 +8066,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.56</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="26">
@@ -7145,7 +8076,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.18</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="27">
@@ -7155,7 +8086,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.43</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="28">
@@ -7165,7 +8096,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
